--- a/data/EW4All_Infrastructure_Member_Update.xlsx
+++ b/data/EW4All_Infrastructure_Member_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wmoomm-my.sharepoint.com/personal/zandreeva_wmo_int/Documents/Desktop/Claude/EW4ALL/RA-II-V/Infrastracture Dashboard/deliverables/repo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0903180316904462315BE0DC4F52C08BD155F159" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A9D1436-4F1D-4D37-A77C-830C5A180E0F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_840009BACB94BF8FA9011CD4FC11BA1FCFFC4DC9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4446240-2B92-4CF5-857C-8D2D6C1E6086}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -875,6 +875,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4165,6 +4169,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{e962d134-526b-49fe-8fc7-dd80537250d0}" enabled="1" method="Standard" siteId="{eaa6be54-4687-40c4-9827-c044bd8e8d3c}" contentBits="0" removed="0"/>
+  <clbl:label id="{e962d134-526b-49fe-8fc7-dd80537250d0}" enabled="1" method="Standard" siteId="{eaa6be54-4687-40c4-9827-c044bd8e8d3c}" removed="0"/>
 </clbl:labelList>
 </file>